--- a/panchang-data/Jyoshimath2026.xlsx
+++ b/panchang-data/Jyoshimath2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5404">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16237,6 +16237,9 @@
   </si>
   <si>
     <t>121°05'03.64</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16726,7 +16729,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16812,7 +16815,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16898,7 +16901,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16984,7 +16987,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17070,7 +17073,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17156,7 +17159,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17242,7 +17245,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17328,7 +17331,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17414,7 +17417,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17500,7 +17503,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17586,7 +17589,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17672,7 +17675,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17758,7 +17761,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17844,7 +17847,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17930,7 +17933,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18016,7 +18019,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18102,7 +18105,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18188,7 +18191,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18274,7 +18277,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18360,7 +18363,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18446,7 +18449,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18532,7 +18535,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18618,7 +18621,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18704,7 +18707,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18790,7 +18793,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18876,7 +18879,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18962,7 +18965,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19048,7 +19051,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19134,7 +19137,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19220,7 +19223,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19306,7 +19309,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19392,7 +19395,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19478,7 +19481,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19564,7 +19567,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19650,7 +19653,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19736,7 +19739,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19822,7 +19825,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19908,7 +19911,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19994,7 +19997,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20080,7 +20083,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20166,7 +20169,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20252,7 +20255,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20338,7 +20341,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20424,7 +20427,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20510,7 +20513,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20596,7 +20599,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20682,7 +20685,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20768,7 +20771,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20854,7 +20857,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20940,7 +20943,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21026,7 +21029,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21112,7 +21115,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21198,7 +21201,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21284,7 +21287,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21370,7 +21373,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21456,7 +21459,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21542,7 +21545,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21628,7 +21631,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21714,7 +21717,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21800,7 +21803,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21886,7 +21889,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21972,7 +21975,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22058,7 +22061,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22144,7 +22147,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22230,7 +22233,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22316,7 +22319,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22402,7 +22405,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22488,7 +22491,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22574,7 +22577,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22660,7 +22663,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22746,7 +22749,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22832,7 +22835,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22918,7 +22921,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23004,7 +23007,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23090,7 +23093,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23176,7 +23179,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23262,7 +23265,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23348,7 +23351,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23434,7 +23437,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23520,7 +23523,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23606,7 +23609,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23692,7 +23695,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23778,7 +23781,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23864,7 +23867,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23950,7 +23953,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24036,7 +24039,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24122,7 +24125,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24208,7 +24211,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24294,7 +24297,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24380,7 +24383,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24466,7 +24469,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24552,7 +24555,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1010</v>
+        <v>1451</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24638,7 +24641,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24724,7 +24727,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24810,7 +24813,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24896,7 +24899,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24982,7 +24985,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25068,7 +25071,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25154,7 +25157,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25240,7 +25243,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25326,7 +25329,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25412,7 +25415,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25498,7 +25501,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25584,7 +25587,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25670,7 +25673,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25756,7 +25759,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25842,7 +25845,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25928,7 +25931,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26014,7 +26017,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26100,7 +26103,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26186,7 +26189,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26272,7 +26275,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26358,7 +26361,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26444,7 +26447,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26530,7 +26533,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26616,7 +26619,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26702,7 +26705,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26788,7 +26791,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26874,7 +26877,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26960,7 +26963,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27046,7 +27049,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1451</v>
+        <v>1873</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27132,7 +27135,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27218,7 +27221,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27304,7 +27307,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27390,7 +27393,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27476,7 +27479,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27562,7 +27565,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27648,7 +27651,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27734,7 +27737,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27820,7 +27823,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27906,7 +27909,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27992,7 +27995,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28078,7 +28081,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28164,7 +28167,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28250,7 +28253,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28336,7 +28339,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1873</v>
+        <v>2310</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28422,7 +28425,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28508,7 +28511,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28594,7 +28597,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28680,7 +28683,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28766,7 +28769,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28852,7 +28855,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28938,7 +28941,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29024,7 +29027,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29110,7 +29113,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29196,7 +29199,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29282,7 +29285,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29368,7 +29371,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29454,7 +29457,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29540,7 +29543,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29626,7 +29629,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1873</v>
+        <v>5403</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29712,7 +29715,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29798,7 +29801,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29884,7 +29887,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29970,7 +29973,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30056,7 +30059,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30142,7 +30145,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30228,7 +30231,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30314,7 +30317,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30400,7 +30403,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30486,7 +30489,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30572,7 +30575,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30658,7 +30661,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30744,7 +30747,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30830,7 +30833,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30916,7 +30919,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2310</v>
+        <v>5403</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
